--- a/output/pdf_financials_xlsx/JTWO.xlsx
+++ b/output/pdf_financials_xlsx/JTWO.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.022009</v>
+        <v>0.03749</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.103753</v>
+        <v>0.286029</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.022009</v>
+        <v>-0.03749</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.103753</v>
+        <v>-0.286029</v>
       </c>
     </row>
     <row r="12">
@@ -2916,14 +2916,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-0.03749</v>
+        <v>0.03749</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.286029</v>
+        <v>0.286029</v>
       </c>
     </row>
     <row r="12">

--- a/output/pdf_financials_xlsx/JTWO.xlsx
+++ b/output/pdf_financials_xlsx/JTWO.xlsx
@@ -514,10 +514,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.022009</v>
+        <v>0.024821</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.103753</v>
+        <v>0.108079</v>
       </c>
     </row>
     <row r="8">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.0047</v>
+        <v>-0.0047</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.0752</v>
+        <v>-0.0752</v>
       </c>
     </row>
     <row r="18">
@@ -2830,7 +2830,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>0.002812</v>
       </c>
@@ -3068,7 +3072,11 @@
           <t>Income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>0.0047</v>
       </c>
